--- a/v4/03_extracted/SituationChap_PREVISION_BEST_2027.xlsx
+++ b/v4/03_extracted/SituationChap_PREVISION_BEST_2027.xlsx
@@ -1906,25 +1906,25 @@
         <v>134</v>
       </c>
       <c r="L13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M13">
-        <v>526.5</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>-616666.67</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>0.1102</v>
+        <v>0.4029</v>
       </c>
       <c r="P13">
-        <v>-67941.87</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>1054422.79</v>
+        <v>0</v>
       </c>
       <c r="S13" t="s">
         <v>237</v>
@@ -2104,19 +2104,19 @@
         <v>231</v>
       </c>
       <c r="N16">
-        <v>-406666.67</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0.7625999999999999</v>
       </c>
       <c r="P16">
-        <v>-310127.03</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>296995.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="s">
         <v>237</v>
@@ -2736,19 +2736,19 @@
         <v>231</v>
       </c>
       <c r="N26">
-        <v>-6086666.67</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0.4721</v>
       </c>
       <c r="P26">
-        <v>-2873245.56</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
       </c>
       <c r="R26">
-        <v>2581608.92</v>
+        <v>0</v>
       </c>
       <c r="S26" t="s">
         <v>237</v>
@@ -4210,19 +4210,19 @@
         <v>100</v>
       </c>
       <c r="N49">
-        <v>-23333.33</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
       </c>
       <c r="R49">
-        <v>52408.59</v>
+        <v>0</v>
       </c>
       <c r="S49" t="s">
         <v>237</v>
@@ -5105,7 +5105,7 @@
         <v>233</v>
       </c>
       <c r="M63">
-        <v>108.8</v>
+        <v>100</v>
       </c>
       <c r="N63">
         <v>133333.33</v>
@@ -6975,25 +6975,25 @@
         <v>213</v>
       </c>
       <c r="L92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M92">
-        <v>332.8</v>
+        <v>100</v>
       </c>
       <c r="N92">
-        <v>-1335438.67</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>0.5161</v>
+        <v>1</v>
       </c>
       <c r="P92">
-        <v>-689204.67</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
       </c>
       <c r="R92">
-        <v>400904.2</v>
+        <v>0</v>
       </c>
       <c r="S92" t="s">
         <v>237</v>
@@ -7238,16 +7238,16 @@
         <v>231</v>
       </c>
       <c r="M96">
-        <v>117.1</v>
+        <v>100</v>
       </c>
       <c r="N96">
-        <v>-333333.33</v>
+        <v>0</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96">
-        <v>-333333.33</v>
+        <v>0</v>
       </c>
       <c r="S96" t="s">
         <v>237</v>
@@ -7607,19 +7607,19 @@
         <v>100</v>
       </c>
       <c r="N102">
-        <v>-1137789</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
       </c>
       <c r="P102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
       </c>
       <c r="R102">
-        <v>5481054.34</v>
+        <v>0</v>
       </c>
       <c r="S102" t="s">
         <v>237</v>
@@ -7796,7 +7796,7 @@
         <v>231</v>
       </c>
       <c r="M105">
-        <v>145.5</v>
+        <v>100</v>
       </c>
       <c r="N105">
         <v>608333.33</v>
